--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-careplan.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/CarePlan</t>
+    <t>http://hl7.org/fhir/StructureDefinition/CarePlan|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -440,7 +440,7 @@
     <t>CarePlan.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -478,7 +478,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -536,7 +536,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -652,7 +652,7 @@
     <t>CarePlan.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|Questionnaire|Measure|ActivityDefinition|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|ActivityDefinition|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -690,7 +690,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1)
 </t>
   </si>
   <si>
@@ -823,7 +823,7 @@
     <t>「これが複数存在する計画の区別を支援するための「種類」の計画である」（たとえば、「在宅医療」、「精神医療」、「喘息」、「疾患管理」など）。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-category</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-category|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -860,7 +860,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -885,7 +885,7 @@
     <t>CarePlan.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -974,7 +974,7 @@
     <t>CarePlan.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|Device|RelatedPerson|Organization|CareTeam)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1008,7 +1008,7 @@
     <t>CarePlan.careTeam</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam)
+    <t xml:space="preserve">Reference(CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -1030,7 +1030,7 @@
     <t>CarePlan.addresses</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition)
+    <t xml:space="preserve">Reference(Condition|4.0.1)
 </t>
   </si>
   <si>
@@ -1061,7 +1061,7 @@
     <t>CarePlan.supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1083,7 +1083,7 @@
     <t>CarePlan.goal</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Goal)
+    <t xml:space="preserve">Reference(Goal|4.0.1)
 </t>
   </si>
   <si>
@@ -1170,7 +1170,7 @@
     <t>活動の結果を特定します。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.0.1</t>
   </si>
   <si>
     <t>CarePlan.activity.outcomeReference</t>
@@ -1222,7 +1222,7 @@
     <t>CarePlan.activity.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment|CommunicationRequest|DeviceRequest|MedicationRequest|NutritionOrder|Task|ServiceRequest|VisionPrescription|RequestGroup)
+    <t xml:space="preserve">Reference(Appointment|4.0.1|CommunicationRequest|4.0.1|DeviceRequest|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|Task|4.0.1|ServiceRequest|4.0.1|VisionPrescription|4.0.1|RequestGroup|4.0.1)
 </t>
   </si>
   <si>
@@ -1293,7 +1293,7 @@
     <t>CarePlan.activity.detail.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Questionnaire|Measure|OperationDefinition)
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1327,7 +1327,7 @@
     <t>活動の種類に関する詳細な説明例：どのような実験、どのプロシジャー（処置等）、どのような受療行動ですか。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1354,7 +1354,7 @@
     <t>看護計画のアクティビティが必要な理由を特定する。一般的な健康状態コード、予防、手術の準備などの概念を含めることができる。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1363,7 +1363,7 @@
     <t>CarePlan.activity.detail.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1484,7 +1484,7 @@
     <t>CarePlan.activity.detail.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1509,7 +1509,7 @@
     <t>CarePlan.activity.detail.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|RelatedPerson|Patient|CareTeam|HealthcareService|Device)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|RelatedPerson|4.0.1|Patient|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1535,7 +1535,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication|Substance)</t>
+Reference(Medication|4.0.1|Substance|4.0.1)</t>
   </si>
   <si>
     <t>何を管理/供給するのですか？</t>
@@ -1547,7 +1547,7 @@
     <t>ケア・プランのアクティビティーの一環として提供される製品またはアレンジメント</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>.participation[typeCode=PRD].role</t>
@@ -1563,7 +1563,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1951,7 +1951,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="163.6796875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1966,7 +1966,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="65.9765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="46.17578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.24609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-careplan.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-careplan.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/CarePlan|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/CarePlan</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -440,7 +440,7 @@
     <t>CarePlan.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -478,7 +478,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -536,7 +536,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -652,7 +652,7 @@
     <t>CarePlan.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|ActivityDefinition|4.0.1|OperationDefinition|4.0.1)
+    <t xml:space="preserve">canonical(PlanDefinition|Questionnaire|Measure|ActivityDefinition|OperationDefinition)
 </t>
   </si>
   <si>
@@ -690,7 +690,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan)
 </t>
   </si>
   <si>
@@ -823,7 +823,7 @@
     <t>「これが複数存在する計画の区別を支援するための「種類」の計画である」（たとえば、「在宅医療」、「精神医療」、「喘息」、「疾患管理」など）。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-category</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -860,7 +860,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
+    <t xml:space="preserve">Reference(Patient|Group)
 </t>
   </si>
   <si>
@@ -885,7 +885,7 @@
     <t>CarePlan.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t xml:space="preserve">Reference(Encounter)
 </t>
   </si>
   <si>
@@ -974,7 +974,7 @@
     <t>CarePlan.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
+    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|Device|RelatedPerson|Organization|CareTeam)
 </t>
   </si>
   <si>
@@ -1008,7 +1008,7 @@
     <t>CarePlan.careTeam</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|4.0.1)
+    <t xml:space="preserve">Reference(CareTeam)
 </t>
   </si>
   <si>
@@ -1030,7 +1030,7 @@
     <t>CarePlan.addresses</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1)
+    <t xml:space="preserve">Reference(Condition)
 </t>
   </si>
   <si>
@@ -1061,7 +1061,7 @@
     <t>CarePlan.supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1083,7 +1083,7 @@
     <t>CarePlan.goal</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Goal|4.0.1)
+    <t xml:space="preserve">Reference(Goal)
 </t>
   </si>
   <si>
@@ -1170,7 +1170,7 @@
     <t>活動の結果を特定します。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/care-plan-activity-outcome</t>
   </si>
   <si>
     <t>CarePlan.activity.outcomeReference</t>
@@ -1222,7 +1222,7 @@
     <t>CarePlan.activity.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Appointment|4.0.1|CommunicationRequest|4.0.1|DeviceRequest|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|Task|4.0.1|ServiceRequest|4.0.1|VisionPrescription|4.0.1|RequestGroup|4.0.1)
+    <t xml:space="preserve">Reference(Appointment|CommunicationRequest|DeviceRequest|MedicationRequest|NutritionOrder|Task|ServiceRequest|VisionPrescription|RequestGroup)
 </t>
   </si>
   <si>
@@ -1293,7 +1293,7 @@
     <t>CarePlan.activity.detail.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Questionnaire|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1)
+    <t xml:space="preserve">canonical(PlanDefinition|ActivityDefinition|Questionnaire|Measure|OperationDefinition)
 </t>
   </si>
   <si>
@@ -1327,7 +1327,7 @@
     <t>活動の種類に関する詳細な説明例：どのような実験、どのプロシジャー（処置等）、どのような受療行動ですか。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -1354,7 +1354,7 @@
     <t>看護計画のアクティビティが必要な理由を特定する。一般的な健康状態コード、予防、手術の準備などの概念を含めることができる。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1363,7 +1363,7 @@
     <t>CarePlan.activity.detail.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
+    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference)
 </t>
   </si>
   <si>
@@ -1484,7 +1484,7 @@
     <t>CarePlan.activity.detail.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location|4.0.1)
+    <t xml:space="preserve">Reference(Location)
 </t>
   </si>
   <si>
@@ -1509,7 +1509,7 @@
     <t>CarePlan.activity.detail.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|RelatedPerson|4.0.1|Patient|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1|Device|4.0.1)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|RelatedPerson|Patient|CareTeam|HealthcareService|Device)
 </t>
   </si>
   <si>
@@ -1535,7 +1535,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication|4.0.1|Substance|4.0.1)</t>
+Reference(Medication|Substance)</t>
   </si>
   <si>
     <t>何を管理/供給するのですか？</t>
@@ -1547,7 +1547,7 @@
     <t>ケア・プランのアクティビティーの一環として提供される製品またはアレンジメント</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
   </si>
   <si>
     <t>.participation[typeCode=PRD].role</t>
@@ -1563,7 +1563,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1951,7 +1951,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="163.6796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="122.921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1966,7 +1966,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="65.9765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.24609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="46.17578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
